--- a/光伏配储项目/电价数据/2026/外海站.xlsx
+++ b/光伏配储项目/电价数据/2026/外海站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.53443</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.37993</v>
+      </c>
+      <c r="C117" t="n">
+        <v>1.20452</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.6376000000000001</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.9787</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.79767</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.70298</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45583</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.44052</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42263</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.45034</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.40822</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.39763</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.39865</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38333</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40151</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42421</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41103</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35292</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39161</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38419</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41543</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39365</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42576</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41239</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42239</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41225</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44549</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.46185</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.3134</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.33939</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.29283</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.31999</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.36497</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.72793</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.5897</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.48167</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.25787</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.37271</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.53066</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.55638</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.24514</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.31447</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.7619600000000001</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.76287</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.75636</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.459</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.14222</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.50445</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.28675</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.29398</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.32187</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.33747</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.50117</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.76502</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.8496699999999999</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.28907</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.56021</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.2929</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.61876</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.6027899999999999</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.7623</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.71072</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.7612000000000001</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.99388</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>1.2968</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>1.43525</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>1.65097</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.64005</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.13441</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.9414400000000001</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.80376</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.95243</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>1.13523</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.91723</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.63531</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.69103</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.36599</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.12097</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.70266</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>1.05704</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>1.17345</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>1.03085</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>1.37612</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>1.14462</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>1.13564</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>1.09394</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.7101499999999999</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.47935</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.4059</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41293</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42216</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32991</v>
+      </c>
+      <c r="C118" t="n">
+        <v>1.05339</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.94778</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>1.02352</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.53612</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5225299999999999</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50624</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.53504</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.49786</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.41046</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.47239</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.388</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38088</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39203</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33759</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.37052</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35565</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.3593</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.37523</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.37519</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.35915</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.38019</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.42098</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.5455099999999999</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.74561</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.72397</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.45746</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.37922</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.43996</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34563</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.38249</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.81014</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.94802</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.58527</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.75918</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.80765</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.69172</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.61715</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.47683</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.4968399999999999</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.60387</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.34406</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.99449</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>1.02224</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>1.30504</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.3727200000000001</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.95336</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>1.20108</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.83968</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.7761699999999999</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>1.16953</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.98641</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.8707699999999999</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>1.40559</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.30833</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.48281</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.57321</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.46721</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.48953</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>1.07849</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.9173300000000001</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.87929</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.9064800000000001</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.8225800000000001</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.74258</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.76217</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.46754</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.85668</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.04055</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>1.01481</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.83651</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.22496</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.45232</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.38987</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.44063</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>1.53886</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.52253</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>1.68564</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>1.07052</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>1.17184</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.75316</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.8930900000000001</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.6443099999999999</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.61621</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.77185</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.44072</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43474</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.41762</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33926</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37738</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35446</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33349</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32156</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.51547</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.4607</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.5376000000000001</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.42946</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.43451</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.4146</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.39819</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.38911</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38202</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36134</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.4336</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.44953</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.3352</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.36975</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39318</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36617</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.3709</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35315</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.35849</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.34842</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36294</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35607</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38003</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39645</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47332</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44992</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.44401</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34803</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39674</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35168</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36805</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.3465</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.60938</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.61642</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.7647999999999999</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.6263200000000001</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.58343</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.59113</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.45009</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.30841</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.31446</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.30212</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.47607</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.38691</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.67986</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.8739600000000001</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>1.20564</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.5931900000000001</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.94855</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>1.25781</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.78183</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.82475</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.66052</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.78295</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.9216299999999999</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.90449</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.66069</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.44143</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.37969</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.39699</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.49977</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.88451</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.8311799999999999</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.92689</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>1.44669</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>1.09719</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>1.10916</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.9322999999999999</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.8753200000000001</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.81867</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>1.22915</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>1.21948</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>1.10064</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>1.06072</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>1.0782</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>1.05453</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>1.00066</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>1.47345</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.8836799999999999</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>1.48661</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.8811100000000001</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.90198</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.8880399999999999</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.9741299999999999</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.90308</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>1.00486</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.84385</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.65412</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.6396799999999999</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.49063</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.38452</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34312</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31992</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.87826</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.57299</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.47801</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.461</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.5105299999999999</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.5658500000000001</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.38512</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.54998</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.32768</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.3665</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.34866</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.46646</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.3489</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.31795</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.34867</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.34858</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.31986</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.32545</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.31627</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.31853</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.31649</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.31321</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.36748</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33921</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35755</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.36957</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.3888</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.33641</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.35788</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.33236</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.34472</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.56088</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.52711</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.63951</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.86542</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.91784</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.6410800000000001</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.98754</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>1.03728</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.61112</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.6991000000000001</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.97254</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.9304</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>1.14395</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.8153899999999999</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.85037</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.51875</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.6395700000000001</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.47005</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.42378</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.51201</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.78479</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.94045</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.7539600000000001</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.78687</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.82456</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.76607</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.7326</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.69655</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.89775</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.94156</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.5784600000000001</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.9085599999999999</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.85561</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.6139</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.78431</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.83052</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.7639</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.85365</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.93176</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.94638</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.9225800000000001</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.94384</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>1.52982</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.8715900000000001</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.8334900000000001</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.7851699999999999</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.8512999999999999</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.88385</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.88054</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.85299</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.80164</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.57969</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.4357200000000001</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.32579</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.5872200000000001</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.31573</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31694</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.31513</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.31041</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.5461</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.45638</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.39769</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.36118</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.34261</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.32204</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32423</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.33042</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.3147</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31533</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.30914</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31612</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31269</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.30808</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.30962</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.3061</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.3083</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.31218</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.31025</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.30611</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.30638</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31311</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31161</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32442</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32432</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.3328</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.3261</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.30921</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.30317</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.28805</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.29925</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.29755</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.19947</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.1949</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.23177</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.195</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.26686</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.15979</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.20109</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.21601</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.35536</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.42443</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.30215</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.34771</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.15762</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.36114</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.15353</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.422</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.34876</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.1543</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.26852</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.26757</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.26068</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.28941</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.22404</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.18707</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.20015</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.19145</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.19122</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.14303</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.15939</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.17468</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>0.15109</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.36234</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.28269</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.33032</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.38272</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.49487</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.4171</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.41847</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.37171</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.41655</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.42711</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.49094</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.37521</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.43231</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.45573</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.40083</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.44606</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.3709</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.39953</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39845</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.40986</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46754</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.36855</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39643</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.40002</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.33995</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35501</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35809</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34469</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35529</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.30632</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.9860399999999999</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.7419</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.7715700000000001</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.5241399999999999</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.50854</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.38242</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.3921</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.38098</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.35125</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.33149</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.33587</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.38073</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.36283</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.36075</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.3454700000000001</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33916</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.32893</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.3357</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.33928</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.33113</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.31996</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.33114</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33532</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.3388</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.35002</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35201</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34244</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31601</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.21388</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.06326</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04659000000000001</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>0.14955</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04571</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04413</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04571</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04433</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04319</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.04185</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.005900000000000001</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.19742</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.04534000000000001</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.04346</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.13766</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.05217</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04295</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04276</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04484</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.04473</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04486</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.01741</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.0423</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04451</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04197</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.04235</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>0.14804</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04442</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04477</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04237</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04347</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.14859</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.14848</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.04982</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>0.15064</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>0.16017</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>0.16604</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>0.16646</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>0.16852</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.30143</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.30006</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.37887</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.34025</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.34419</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.33722</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.37943</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.41474</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.3558</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.34425</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.3556</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.35481</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.35684</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.38126</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.36257</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.36044</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.33779</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.33153</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.34963</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.37921</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.35961</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36749</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36598</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33593</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33126</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.38211</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31672</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.40552</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.34958</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.3217</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.31394</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.31106</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.30086</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.30555</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.3008</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.30283</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.29966</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.29304</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.28968</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.29638</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.24663</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.2391</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17179</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14841</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.16013</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15937</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23742</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21479</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.26869</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.28757</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.29848</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.3039</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.32028</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.30627</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.30076</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.30293</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.30268</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.29868</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.3039</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32354</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.32245</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.32543</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.36309</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.59424</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.6980599999999999</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.55231</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.52567</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.57705</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.62314</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.76351</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.48135</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.35182</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.45799</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.62013</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.61358</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.71941</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.49675</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.45477</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.40085</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.39766</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.14323</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.30426</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31806</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.34841</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31735</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.35441</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.58063</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.58068</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.53252</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.5275599999999999</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.48011</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.65228</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.7960900000000001</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.72725</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.53122</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.65759</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.93753</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>1.23848</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.7227899999999999</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>1.25742</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>1.22932</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.64711</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.6493099999999999</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>1.21912</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.90023</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.59752</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>1.21652</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>1.62505</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.6241</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.30809</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.69904</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.80455</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.53035</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.78762</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.7883600000000001</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8785700000000001</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.8809900000000001</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.50589</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.41203</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.41631</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.46452</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.22342</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87937</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55135</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.6393</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.5424</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.5021100000000001</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45766</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42599</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43991</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45042</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.39231</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45261</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.42043</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.35378</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.39993</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36509</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38824</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41494</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43395</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34402</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39035</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.34816</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.35327</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.34803</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.35108</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.40534</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.3529</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.4507</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.35575</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.39206</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.39996</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.5943999999999999</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.4331</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.59623</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.5858300000000001</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.66518</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.7813600000000001</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.55504</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.55636</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.5335</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>1.24614</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.85156</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>1.12211</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.09977</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>1.07124</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.46138</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.62421</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.46382</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.5131100000000001</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.4533</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.7355499999999999</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.64795</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.54534</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.49534</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.46949</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.76961</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.6450499999999999</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>1.27846</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.5172</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.5284800000000001</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.4167</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.49958</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.49231</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.51642</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.5361900000000001</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.4909</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.51373</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.52691</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.4858</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.51314</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.50968</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.45235</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.50292</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.52462</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.6043999999999999</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.51451</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.59829</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.52716</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.52247</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.5346799999999999</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.51502</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.50351</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.49162</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.49931</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.43793</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.37331</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.4627</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.41232</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45208</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.41467</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.39118</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.37462</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.35307</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32927</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.95589</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36057</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.47618</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.40689</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.47827</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.54059</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.39171</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.40943</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.39004</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.40785</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.3819</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.35346</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.37833</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33069</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35926</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.34579</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32306</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.39991</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.50007</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.3572</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38768</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34357</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35092</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.3553</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37063</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35772</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36285</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31632</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31347</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33246</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.55432</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.38777</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.47018</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.50425</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.5758099999999999</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.67472</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.8236</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.65185</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.40214</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.75774</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.6487999999999999</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.72112</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.6595299999999999</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.52599</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.62906</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.75566</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.30401</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.42829</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.41032</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.39517</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.34377</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.35283</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.6803400000000001</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>1.06356</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.6935</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.5609</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.8852000000000001</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.6225599999999999</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.63461</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.51187</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>1.09679</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.58951</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.35549</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.35828</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.37496</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.37293</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.32396</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.36594</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.30455</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35002</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.3255</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.38595</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.37802</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.34139</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.44492</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.39209</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.495</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.32878</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.42559</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.33581</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.42072</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.82557</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.4325</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.38837</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.32027</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.38626</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44783</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.33328</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.42043</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35896</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40171</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.40044</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.59674</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="C126" t="n">
+        <v>1.05912</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.70403</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.34639</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.70356</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.79531</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.64976</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.58361</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.45044</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45034</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.50049</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.4399</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43746</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41504</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42352</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.50054</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43408</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43413</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.39041</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42802</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.45041</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39631</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.4235</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43412</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.40027</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42354</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.3966</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.40249</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.68624</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.41144</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.61134</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>1.66377</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.84696</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.6942999999999999</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.5236499999999999</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>1.02997</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.55203</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>1.03557</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.36926</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>1.35156</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.93708</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>1.0907</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.68235</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.47943</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>1.12514</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.9931599999999999</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.79161</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.7749299999999999</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.7514700000000001</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.79423</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>1.1808</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.99721</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.34759</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.47888</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.6319199999999999</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.9773999999999999</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.5694900000000001</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.78046</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.75812</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.65626</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.6974</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.6795099999999999</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.81426</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.82884</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.6788999999999999</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.8385499999999999</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>1.08812</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.76537</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.76179</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.8492499999999999</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.72729</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.74761</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>1.06506</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.73915</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.75014</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.8185</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.70194</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.68956</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>1.27384</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.8633099999999999</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>1.42674</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>1.17826</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.7763600000000001</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.7783300000000001</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.62805</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38651</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.36961</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33457</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.34093</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32955</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.3247</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31897</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.4307</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.33915</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.34396</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.3399</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33594</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.32615</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.32941</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.3262</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.32491</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.32411</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.31013</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.32743</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.32615</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.31993</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.31598</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.32013</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.3201</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.31019</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.32512</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.31118</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.31921</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.32049</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.3913</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32505</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.39999</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.37498</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.34993</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33881</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.35472</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33218</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.33456</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.31899</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.37175</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.33588</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.37146</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.32402</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.35253</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.32975</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.30527</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.25516</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.2639</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.31501</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.28722</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>0.70972</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>0.65549</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.23731</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.25257</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.31701</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.29595</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.36301</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.32159</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.37954</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.38164</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.28683</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.27999</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.29575</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.30581</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.27564</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.31976</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.25742</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.32112</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.33936</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.34388</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.35515</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.53011</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.35201</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.38819</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.36167</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.40561</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34363</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.37993</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.3466</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.40025</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.3607</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.3849</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.44955</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.39961</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.39356</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.40187</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39771</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.44968</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.4399</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.43927</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.44419</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44427</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.40247</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.39033</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39752</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.3916</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.35973</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.36038</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34804</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34933</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.33969</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.54231</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.38897</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.46868</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42385</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41592</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.37013</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.38108</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.3802</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.39293</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.37959</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.3696</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.37997</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.35976</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.39081</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.37002</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.38003</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.35027</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.34707</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35526</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34489</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.3400899999999999</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.34501</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.3400899999999999</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.34448</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.35487</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.36991</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.37985</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.35971</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.33976</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.34004</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.34032</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32933</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.34642</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.35153</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.3754</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.29192</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.31512</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31492</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.32141</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.29004</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.30214</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.42392</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.27683</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.59427</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.37144</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.28765</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.27529</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.27895</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.29886</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.29553</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31483</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.29631</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.30173</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.37246</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.30459</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.31144</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.29484</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.28634</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.3189</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.31925</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.32998</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.30494</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.33239</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.40341</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.52451</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.47551</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.47257</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.5751799999999999</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.77344</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.7273200000000001</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.58272</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.39901</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.37091</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.3936</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.527</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.63452</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.7446200000000001</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.73377</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.61168</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.44488</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.40898</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.39078</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.37625</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.36677</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.41951</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.39222</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.42061</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.40899</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.39276</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.39447</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38036</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38532</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.36025</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.34019</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36606</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.41863</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37069</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.48339</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.38048</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35276</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.36023</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35176</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34198</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.34779</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.3458</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.34907</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.34617</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.34908</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.34005</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.34124</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.34286</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33802</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.33801</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.33983</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33061</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.34239</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.35316</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.3493</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.37111</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.41803</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.36393</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.55314</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.34252</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.37289</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.68479</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.6864</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.6751200000000001</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.6774199999999999</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.96277</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.96101</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.61527</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.73025</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>1.12354</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.6571900000000001</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>1.1077</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.98781</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.98053</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>1.0479</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.37979</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.77462</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.29148</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>1.20591</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.42127</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.76746</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.36443</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.74249</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.66835</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.9801299999999999</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.96321</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.99663</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>1.00998</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>1.0051</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.98224</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>1.00669</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.775</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>1.03982</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>1.23769</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>1.12121</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>1.13721</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>1.03678</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>1.04452</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>1.05261</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.99129</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>1.0869</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.6650700000000001</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.7222799999999999</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>1.03061</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>1.03898</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>1.03288</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>1.63629</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>1.11231</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>1.42916</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>1.06251</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>1.19323</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.59512</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.50964</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.40327</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>1.5818</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>1.07744</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.6987000000000001</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.34463</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.34317</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.408</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.32918</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.34542</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.32742</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.32203</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.33351</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.32258</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.4237</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.72485</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.34714</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.33162</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.33796</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.36069</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.34111</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.3358</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.33904</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.33274</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.32879</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32636</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.32743</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.33012</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.33095</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.32605</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32083</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31973</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.32635</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.33012</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33516</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.34593</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.34074</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.34338</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.33792</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33873</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.32893</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.33702</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.34067</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.57041</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.57489</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.33998</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.37915</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.54922</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.40794</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.42429</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.42527</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.33825</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.29229</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.34225</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.34168</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.29947</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32549</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28263</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.33207</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.32972</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.32177</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.33279</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32848</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33353</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.33809</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.32315</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.33463</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.33307</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.32857</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.36374</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.40399</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.63315</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.90728</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.77389</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.62422</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.54457</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.39561</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.36322</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.35006</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.41148</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.4145</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.41994</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.40191</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.43727</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.36762</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.3615</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.3678</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.36242</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.3731</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.36203</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.39288</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38553</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37162</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.40288</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35499</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.37991</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.36943</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36097</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.35025</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.34934</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.3493</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.33957</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35129</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.3553</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.3554</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.35135</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35084</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.34944</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34939</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34624</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.35973</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.3470299999999999</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.34963</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33704</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.33957</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.34004</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.3396</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.36929</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32438</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.3383</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.33957</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.34947</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33665</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.33962</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34504</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33588</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33633</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.34011</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.32806</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.34852</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.37477</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.33891</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.37297</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.29543</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.33598</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32978</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.32808</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.33292</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.3237</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.32754</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.32335</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.32099</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.33801</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32593</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32967</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31878</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37107</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.33333</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.38918</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.54827</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.37532</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.42643</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>1.0519</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.418</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.36663</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.37426</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.38191</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.34299</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.33183</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.34022</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34561</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.39255</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.56304</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.3892</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.3546</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.39284</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.41368</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.35168</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.38203</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.3473</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.36029</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.36022</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36226</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.3502</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.53389</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.41727</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.41894</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38363</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.42986</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.40915</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.38574</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.38504</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.6519199999999999</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.83096</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.47181</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.40119</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.45942</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.3934</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.35067</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35096</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35957</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.33988</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.34477</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.31277</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.41065</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.3757</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.37077</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.36101</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.35907</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35909</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.36228</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.35886</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.36052</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.35943</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35357</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36062</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.3608</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35679</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35235</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35977</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.3601</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35977</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.33982</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37085</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35879</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.3565</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.37946</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36587</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.3799</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35653</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35649</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35113</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35182</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35815</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34972</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.32988</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.35048</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.38927</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.42617</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.34545</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.35447</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.5509400000000001</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.31716</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.31638</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.28415</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.52591</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.30718</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.33785</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.31515</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.67259</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.16336</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.3971</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.28851</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.3187</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.32052</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.35352</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.24898</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.41181</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.25827</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.33147</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.33867</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.50632</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.39591</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.39961</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.37306</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.6952699999999999</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.5924199999999999</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.9349500000000001</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.37292</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.7633</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.18058</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.29223</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.59274</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.76367</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.5414500000000001</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.78788</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.7371</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.56799</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>1.11405</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.68063</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.8696799999999999</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.5021100000000001</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.96835</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.21581</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.2445</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.5485099999999999</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.36808</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.89659</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>1.0633</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.86139</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.42982</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.41874</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.37775</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37431</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.3673</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.36015</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34536</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.64393</v>
+      </c>
+      <c r="D133" t="n">
+        <v>1.10719</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.9213600000000001</v>
+      </c>
+      <c r="F133" t="n">
+        <v>1.66804</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.41943</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.41546</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.40474</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.41099</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.40867</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.41754</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.39986</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.39555</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.41132</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.40905</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.39343</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38674</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.41828</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.38692</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.41646</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.38995</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.39977</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.39973</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.41231</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.39985</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.45041</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.44947</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.5604199999999999</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.50054</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.45059</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.4505</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.44029</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>1.07596</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>1.54217</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>1.64002</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>1.71326</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>1.42899</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>1.38108</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>1.55588</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>1.43965</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>1.47672</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.55528</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.7535700000000001</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.7154700000000001</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.78322</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>1.29236</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>1.69868</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>1.61031</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>1.33721</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>1.2776</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>1.19859</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>1.10552</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.79853</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.7123700000000001</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>1.05413</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.43806</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.43757</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.48777</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.50561</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.6207699999999999</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.8694</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.5852999999999999</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.74573</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.56917</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.76346</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.7601599999999999</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>1.21206</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>1.17031</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.8930900000000001</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.89423</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>1.02397</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>1.02572</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>1.37869</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>1.65943</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>1.47556</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>1.07533</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>1.19616</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>1.71038</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>1.67653</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.9106000000000001</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>1.09583</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.8000700000000001</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.47803</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.47142</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.41937</v>
+      </c>
+      <c r="C134" t="n">
+        <v>1.0114</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.6161599999999999</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.48747</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.45804</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.43676</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.42655</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.44836</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.41783</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.40083</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.4577</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39934</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40705</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.39863</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38855</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.37992</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.37487</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35688</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36586</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.37681</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37125</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.3602</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35984</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36586</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38658</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.39025</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.37958</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.36648</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36137</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35512</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37961</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.42795</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.44771</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.39766</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.48994</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.39439</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.3866</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35163</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.36854</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.4521</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.58894</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.5642999999999999</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.56709</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.90559</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.83482</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>1.17754</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>1.10968</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.6952200000000001</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.7417899999999999</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.7524999999999999</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.45761</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.38241</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>1.68541</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.3434700000000001</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.32615</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.31129</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32395</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35262</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.36347</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.34943</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.39351</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.44651</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.43611</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.46728</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.46796</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.4377799999999999</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.36368</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.41298</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.42735</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.49803</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.47915</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.53743</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.38274</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.38688</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.40609</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.4025</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34408</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.36545</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37799</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.39924</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.37947</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35508</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.39964</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.38133</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37501</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.36027</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39387</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.37906</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36415</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.33116</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.62397</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.80143</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.5186499999999999</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.431</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.40746</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.37706</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.35051</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.37703</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.3914</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.35624</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.3573</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.35125</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.35745</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.3474100000000001</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.35118</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.34858</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.37368</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.33144</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.33973</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.34038</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33547</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.34048</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.34548</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.3309</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.33049</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.33745</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.33751</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.36501</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.33528</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.32923</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.32717</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.32709</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.3969</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.33842</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.33049</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.32925</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.29656</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.32687</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.33984</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.29308</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.301</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.17689</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.30506</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.30084</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.32077</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.26811</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.24747</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04336</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.31899</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.17288</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.24709</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.25997</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.18594</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.32594</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.22241</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.28333</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.28324</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.23623</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.26669</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.30055</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.37818</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.28397</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.33574</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.35495</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.33066</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.38579</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.3466</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.4049700000000001</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.51187</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.44264</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.39948</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.37027</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.43803</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.42348</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.41254</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.33371</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.48833</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.38146</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.44354</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.40182</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.39892</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.40052</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.38771</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.41101</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.402</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.44108</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.35727</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.36494</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.36964</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.37586</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.34931</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.34987</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.34968</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.35012</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.35168</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.32295</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.569</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.3383</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.3482</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.3532</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.33088</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.32456</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.31948</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.31916</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.31048</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.31027</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.31512</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.31059</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.31096</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.31096</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.31089</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.31662</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.3068</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.30681</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.30929</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.3099</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.30614</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.3068</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.3074</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.3105</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.31136</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.30703</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.31133</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.31294</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.19938</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.25406</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.39507</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.22787</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.22004</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.17859</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>0.16312</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.24641</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.16058</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>0.17678</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>0.15749</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>0.2053</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>0.49073</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>0.23612</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>0.21193</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>0.17001</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>0.16043</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>0.19905</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>0.15268</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>0.17234</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>0.15957</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>0.1529</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>0.17906</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.37018</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.2913</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>0.15183</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>0.15972</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>0.15185</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>0.16376</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>0.15969</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>0.16087</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>0.26156</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>0.19959</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.26929</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.27117</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.31673</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.31067</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.31883</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.33226</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.31117</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.31899</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.33269</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.3522</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.33013</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.34467</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.33027</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.3278</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.34423</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.34069</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.3394</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.34608</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.33453</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.34721</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.33691</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.37256</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.61905</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.34826</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.39713</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.34656</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.33194</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.336</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.32803</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.33099</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.29604</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.30139</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.30481</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.8043400000000001</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.79826</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.39253</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.47111</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.39598</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.52512</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.49344</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.40751</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.3511</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.34981</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.33861</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.32106</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.31789</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.31766</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.31728</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.32527</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.39779</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.30024</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.33883</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.32561</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.35205</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.31957</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.34192</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.3396</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.37574</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.59293</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.37502</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.33531</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.53384</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.31291</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.3275</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.8837699999999999</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.88681</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>1.0049</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.85084</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.65991</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.9012</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.41466</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.40679</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.26332</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.29925</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>-0.0002</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.4347</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.40408</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.33423</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.35233</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.20972</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0.15949</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.4192</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.44887</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.29824</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.16709</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.30562</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.6491399999999999</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.48923</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.33647</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.44824</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.75425</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>1.346</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.37349</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.59415</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.52496</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.8964</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.70866</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.70956</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.71682</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.72436</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.85172</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.5391900000000001</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.7546900000000001</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.5724199999999999</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.78059</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>1.17263</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>1.17313</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>1.20617</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>1.59191</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>1.17308</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>1.26447</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>1.33601</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.69239</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.89481</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.75618</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.80588</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.80344</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>1.09895</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.94935</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.74353</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.37562</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.35956</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.57369</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.36825</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.33662</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.3302</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.47142</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.61766</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.4615</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.57586</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.57672</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.4624</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.41043</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.40452</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.37613</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.38615</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.38628</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.34877</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.35528</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.34333</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34646</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.25382</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.35904</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.35029</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.34269</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.34286</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.34689</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.35963</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.38279</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.37464</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.39053</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.85793</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.70878</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.64323</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.5997</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.48955</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.5625599999999999</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.51462</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.49718</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.2166</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.72112</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.87213</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.7846900000000001</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.87497</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>1.19621</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>1.19087</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.79577</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.8136599999999999</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.58057</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.44537</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.4476</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.49827</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.39663</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.22759</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.4528</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.44382</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.44381</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.37256</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.51402</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>1.01927</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.65484</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.39351</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.44621</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.40952</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.41844</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.41124</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.42355</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.41527</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.42945</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.46867</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.46712</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.47217</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.43945</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.45046</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.38776</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.39067</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.36881</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.40608</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.45093</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.47288</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.5376299999999999</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.85815</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.81489</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.5371900000000001</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.46737</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.96787</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.6689400000000001</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.57216</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.85775</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.70605</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.45648</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.45994</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.44768</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.409</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.45612</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.35819</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.37018</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.339</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.33892</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.33854</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.37038</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.42523</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.40979</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.38601</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.38526</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.37676</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.38333</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.34825</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.36789</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.38206</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.36188</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.35259</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.34913</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.35241</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.34818</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.36081</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.34574</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.34471</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.34326</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34651</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.34421</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.34606</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.35833</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.33473</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.36912</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.3593</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.37975</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35942</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.5224299999999999</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.5859500000000001</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.37595</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.54704</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.80013</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>1.03912</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>1.42933</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>1.65532</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>1.79797</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.63942</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.75417</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.79288</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.74138</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.7141000000000001</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.7478899999999999</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.72656</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.7158</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.71897</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.34031</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>1.10858</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.46052</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.7096399999999999</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.4987200000000001</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.72253</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.72919</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>1.59583</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.7110299999999999</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.60034</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.72378</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.70284</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.72778</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.9834700000000001</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>1.13788</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>1.16042</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>1.20779</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>1.27454</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>1.2576</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>1.3274</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>1.33986</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>1.31776</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.94902</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.8428099999999999</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.8076599999999999</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.47939</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>1.00883</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.7788200000000001</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.86287</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.73766</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.67952</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.66555</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.66669</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.6375599999999999</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.4242</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.6854</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.54545</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.40177</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.45847</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.56675</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.38014</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.63406</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.5980599999999999</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.32322</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.37271</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.36281</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.36868</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34704</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.67145</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.40119</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.40123</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.39189</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.38075</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.36014</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.37554</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37442</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37864</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.3773</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36916</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36692</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36153</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.36004</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35978</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.3604</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.35586</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32884</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35618</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.35105</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.34723</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.35016</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.36014</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.37103</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.39959</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.37576</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.36966</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.37295</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.40169</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.44444</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.38346</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.6849400000000001</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.55721</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.6929</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.61427</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.61591</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.52973</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>1.52592</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>1.54484</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.79508</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.6475299999999999</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.79389</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.72454</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.80192</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.7847000000000001</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.78484</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.36631</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>1.04925</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>1.06818</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.76164</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.49809</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.33603</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.35038</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.56786</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.28057</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.59558</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.6729400000000001</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.6556000000000001</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.68938</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>1.14805</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>1.15019</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>1.49118</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>1.17104</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>1.49482</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>1.47647</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>1.50844</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>1.27641</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>1.20107</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.87687</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.8573999999999999</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>1.53743</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>1.61087</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>1.31485</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>1.31619</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>1.13859</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>1.52395</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>1.61462</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>1.59076</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>1.07536</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.9894500000000001</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.74194</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>1.28509</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>1.26349</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>1.53983</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>1.30675</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>1.30853</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.39829</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.64754</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.6297999999999999</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.61429</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.3948</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.36946</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.37506</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.2708</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.35825</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.37041</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.35308</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.34743</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.34986</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.34243</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.3484</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.57394</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.35018</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.34489</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.39744</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.35865</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.34972</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.35498</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.3389</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.34514</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.34152</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.33852</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.34011</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.33734</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.33656</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.34257</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.32965</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.36089</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.43944</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.34486</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.32177</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.32496</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.31262</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.35203</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.5572</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.8276699999999999</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.66835</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.59817</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.6245499999999999</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.79715</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.8010700000000001</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.9426599999999999</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.52867</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.41812</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>1.24983</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.99202</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.9414199999999999</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.61437</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.42869</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.1495</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.36764</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.52924</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>1.31079</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.16209</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.6056699999999999</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.2111</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.60846</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.6942699999999999</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.59917</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.30874</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.70314</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.50307</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.4111</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.80459</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.6529199999999999</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.5490499999999999</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.72303</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.5876</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.7182500000000001</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.8040700000000001</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.85948</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.72223</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.73321</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.7093200000000001</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.71469</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.7252999999999999</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>1.13574</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>1.19344</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>1.06215</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>1.08128</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>1.25147</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>1.00773</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>1.03039</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.7840199999999999</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.76446</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.77923</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.8177000000000001</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.81699</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.7982899999999999</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.91007</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.6031799999999999</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.5792200000000001</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.5244099999999999</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.5045500000000001</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.41328</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.37844</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.37535</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.35013</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1.27335</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.86368</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.89318</v>
+      </c>
+      <c r="F142" t="n">
+        <v>1.14534</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.73227</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.41747</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.44513</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.37081</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.39097</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.37566</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.37371</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.36148</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.37857</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.37039</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.37851</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.38225</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.37984</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.37109</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.3716</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.36599</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.37085</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.3708</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.3668</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.36733</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.3503</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.38107</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.35804</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.6075700000000001</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.35984</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.34277</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.33263</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.33162</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.49122</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.5781499999999999</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.57739</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.54448</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.6851499999999999</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.5829099999999999</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.69064</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>1.20262</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.72877</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.79434</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.89274</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.8809900000000001</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.7799299999999999</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.9876</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.74373</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.42102</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>1.14787</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.40407</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.35483</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.75312</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.49851</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.59572</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.76242</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.5740299999999999</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.36703</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.42781</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.50654</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>1.01261</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.82048</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.56645</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>1.22153</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.8054</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.7708400000000001</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>1.26267</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>1.21065</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>1.02711</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.8631</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.82635</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.83751</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.8359500000000001</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.8615700000000001</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.8604400000000001</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.89022</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>1.27825</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>1.31874</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>1.40987</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>1.77772</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.81449</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.83699</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.8140599999999999</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.8599199999999999</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>1.55452</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>1.01193</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.60451</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.58182</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.47482</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.35482</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.94924</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.6192300000000001</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.62109</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.43631</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.46164</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.46323</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.4404</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.44949</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.41963</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.43256</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.43848</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.37331</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.40075</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.40017</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35015</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.3335</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.35102</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.35038</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.32895</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.34212</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.34161</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.36451</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.35051</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.39604</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.36975</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.3497</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.36094</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.36748</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.39473</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.3759</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.38419</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.36243</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.32276</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.36935</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.68601</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.5373300000000001</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.79364</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>1.05574</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.7529199999999999</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.7920199999999999</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.36331</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.50681</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.48289</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.38714</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.45231</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>1.5089</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.31701</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>1.00829</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.6281599999999999</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.3908</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.35483</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.33117</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.39477</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.3833</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.4505</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.31006</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.54403</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.4821</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.6360800000000001</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.50525</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.41848</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.81491</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.69025</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.70012</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.72799</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.7489</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.55763</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.53501</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.52098</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.5345</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.5407999999999999</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.5561</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.6197</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.62539</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.5239400000000001</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.6194700000000001</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.63486</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.91437</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.6583300000000001</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.57841</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.5715</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.55422</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.51874</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.5187200000000001</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.65016</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.6283</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.6747799999999999</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.55763</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.51879</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.4706</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.45204</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.40852</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.40969</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.38406</v>
       </c>
     </row>
   </sheetData>
